--- a/performance_tracking_forms/017_task_assignment_form--performance_tracking_forms.xlsx
+++ b/performance_tracking_forms/017_task_assignment_form--performance_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'jim_smith'}</t>
+          <t>jim_smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Jim Smith'}</t>
+          <t>Jim Smith</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'task_a'}</t>
+          <t>task_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Task A'}</t>
+          <t>Task A</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'task_b'}</t>
+          <t>task_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Task B'}</t>
+          <t>Task B</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'task_c'}</t>
+          <t>task_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Task C'}</t>
+          <t>Task C</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
